--- a/task/RC/Resources/PigeonStatusInstructionsConditions.xlsx
+++ b/task/RC/Resources/PigeonStatusInstructionsConditions.xlsx
@@ -711,7 +711,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>This bar shows how many steps you have left. Every step Petey takes uses one step. Starting each trial also uses 5 steps, and each incorrect answer uses 10 extra steps. Once you have used up all your steps, the block will end.</t>
+          <t>This bar shows how many steps you have left. Every step Petey takes uses one step, and each incorrect answer uses 15 extra steps. Once you have used up all your steps, the block will end.</t>
         </is>
       </c>
       <c r="B9" t="b">
